--- a/translators/xlsx/tests/sample_condformat.xlsx
+++ b/translators/xlsx/tests/sample_condformat.xlsx
@@ -105,5 +105,17 @@
   <conditionalFormatting sqref="B1:B3">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C10">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>